--- a/data/raw/inventory/Week 32/Audio_Array/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 32/Audio_Array/Seller FBA Inventory (SP-API).xlsx
@@ -520,10 +520,10 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F2" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -538,7 +538,7 @@
         <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="L2" t="n">
         <v>3</v>
@@ -3747,7 +3747,7 @@
         <v>14</v>
       </c>
       <c r="F54" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -3759,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K54" t="n">
         <v>15</v>
@@ -7464,7 +7464,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F114" t="n">
         <v>10</v>
@@ -7479,10 +7479,10 @@
         <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K114" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
@@ -8211,7 +8211,7 @@
         <v>24</v>
       </c>
       <c r="F126" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -8223,7 +8223,7 @@
         <v>0</v>
       </c>
       <c r="J126" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K126" t="n">
         <v>25</v>
@@ -8704,25 +8704,25 @@
         </is>
       </c>
       <c r="E134" t="n">
+        <v>1</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0</v>
+      </c>
+      <c r="J134" t="n">
+        <v>1</v>
+      </c>
+      <c r="K134" t="n">
         <v>2</v>
-      </c>
-      <c r="F134" t="n">
-        <v>0</v>
-      </c>
-      <c r="G134" t="n">
-        <v>0</v>
-      </c>
-      <c r="H134" t="n">
-        <v>0</v>
-      </c>
-      <c r="I134" t="n">
-        <v>0</v>
-      </c>
-      <c r="J134" t="n">
-        <v>2</v>
-      </c>
-      <c r="K134" t="n">
-        <v>3</v>
       </c>
       <c r="L134" t="n">
         <v>1</v>
